--- a/output/erp_upload_list.xlsx
+++ b/output/erp_upload_list.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ERP_업로드목록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="26.8" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[Blue][&gt;=1]+#,##0;[Red][&lt;0]-#,##0;0"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -76,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -88,6 +90,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -455,25 +460,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="8.380000000000001" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="32" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="35" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -484,590 +489,389 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>발주번호</t>
+          <t>배송요청일</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>거래처</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>거래처명</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>품번</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>납품처(매장명)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>품명</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>규격</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>모델명</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>수량</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>매입단가</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>매입합계</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>수주단가</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>수주합계</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>예상마진</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>수령인</t>
-        </is>
-      </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>연락처</t>
+          <t>배송방법</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>배송지주소</t>
+          <t>현장담당자</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>비고</t>
+          <t>배송장소</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>PO-20260818-002</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>한빛지류</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>BK-102</t>
-        </is>
-      </c>
+          <t>8.24 (월)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>친환경 중질지 내지</t>
+          <t>빅뱅</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>B5 / 80g</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>300</v>
+          <t>스타리온 1200 반찬냉장고 1/3 앞작업대 + 1200 2단선반 ★★★</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>SRV12EIEVF</t>
+        </is>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>360000</v>
+        <v>638000</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>2000</v>
+        <v>638000</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>600000</v>
+        <v>708900</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>240000</v>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>이영희</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>010-8888-9999</t>
+        <v>708900</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>70900</v>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>스타리온 직배송 요청</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>경기도 파주시 문발로 456</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr"/>
+          <t>010-4035-1709</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>경기도 남양주시 화도읍 마석중앙로 40, 1층</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>PO-20260818-002</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>한빛지류</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>PAPER-A4</t>
-        </is>
-      </c>
+          <t>8.24 (월)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>프리미엄 복사용지</t>
+          <t>빅뱅</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>A4 / 80g</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>20</v>
+          <t>스타리온 45BOX 냉동냉장 / 하냉동 / 메탈 / 직냉식</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>SR-E45B2FD</t>
+        </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>4500</v>
+        <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>90000</v>
+        <v>964400</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>6500</v>
+        <v>964400</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>130000</v>
+        <v>1071600</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>이영희</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>010-8888-9999</t>
+        <v>1071600</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>107200</v>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>스타리온 직배송 요청</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>경기도 파주시 문발로 456</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
+          <t>010-4035-1709</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>경기도 남양주시 화도읍 마석중앙로 40, 1층</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>PO-20260818-003</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>동서제본</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>BK-201</t>
-        </is>
-      </c>
+          <t>8.24 (월)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>맞춤형 스프링철 제본</t>
+          <t>빅뱅</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>15mm 원형</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>200</v>
+          <t>스타리온 1500 냉동냉장 / 직냉식</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>SR-T15B1F</t>
+        </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>2500</v>
+        <v>1</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>500000</v>
+        <v>686700</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>4000</v>
+        <v>686700</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>800000</v>
+        <v>763000</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>300000</v>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>박민수</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>010-5555-1234</t>
+        <v>763000</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>76300</v>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>스타리온 직배송 요청</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 센텀중앙로 78</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr"/>
+          <t>010-4035-1709</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>경기도 남양주시 화도읍 마석중앙로 40, 1층</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PO-20260818-002</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>한빛지류</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>BK-102</t>
-        </is>
-      </c>
+          <t>8.24 (월)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>친환경 중질지 내지</t>
+          <t>빅뱅</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>B5 / 80g</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>300</v>
+          <t>스타리온 1500 올냉동 / 직냉식</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>SR-T15BAFC</t>
+        </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1200</v>
+        <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>360000</v>
+        <v>692400</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>2000</v>
+        <v>692400</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>600000</v>
+        <v>769300</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>240000</v>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>이영희</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>010-8888-9999</t>
+        <v>769300</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>76900</v>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>스타리온 직배송 요청</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>경기도 파주시 문발로 456</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
+          <t>010-4035-1709</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>경기도 남양주시 화도읍 마석중앙로 40, 1층</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>PO-20260818-002</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>한빛지류</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>PAPER-A4</t>
-        </is>
-      </c>
+          <t>8.24 (월)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>프리미엄 복사용지</t>
+          <t>빅뱅</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>A4 / 80g</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>20</v>
+          <t>음료아날로그</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>SR-SC44RW</t>
+        </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4500</v>
+        <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>90000</v>
+        <v>355000</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>6500</v>
+        <v>355000</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>130000</v>
+        <v>394500</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>40000</v>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>이영희</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>010-8888-9999</t>
+        <v>394500</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>39500</v>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>스타리온 직배송 요청</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>경기도 파주시 문발로 456</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>PO-20260818-003</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>동서제본</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>BK-201</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>맞춤형 스프링철 제본</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>15mm 원형</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>200</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>500000</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>4000</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>800000</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>300000</v>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>박민수</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>010-5555-1234</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>부산광역시 해운대구 센텀중앙로 78</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>PO-20260818-515</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>010-2111-555</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>010-2111-555</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>010-2111-5555</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>서울특별시 강동구 천호동 500-1
-010-2111-5555
-stsasd 냉장고 직냉형</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>PO-20260818-809</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>010-5555-468</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>010-5555-468</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>010-5555-4687</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>서울 강남구 논현동 401-5
-010-5555-4687
-8월 24일
-STASDFG 직냉 냉장고 
-SGDGSQ 직냉동고 양문형
-각 1대</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
+          <t>010-4035-1709</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>경기도 남양주시 화도읍 마석중앙로 40, 1층</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/erp_upload_list.xlsx
+++ b/output/erp_upload_list.xlsx
@@ -16,10 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[Blue][&gt;=1]+#,##0;[Red][&lt;0]-#,##0;0"/>
-  </numFmts>
-  <fonts count="3">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,10 +30,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -52,7 +46,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -60,40 +54,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CBD5E1"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CBD5E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CBD5E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CBD5E1"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -460,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -563,316 +531,6 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>8.24 (월)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>빅뱅</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>스타리온 1200 반찬냉장고 1/3 앞작업대 + 1200 2단선반 ★★★</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>SRV12EIEVF</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>638000</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>638000</v>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>708900</v>
-      </c>
-      <c r="L2" s="4" t="n">
-        <v>708900</v>
-      </c>
-      <c r="M2" s="5" t="n">
-        <v>70900</v>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>스타리온 직배송 요청</t>
-        </is>
-      </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>010-4035-1709</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>경기도 남양주시 화도읍 마석중앙로 40, 1층</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>8.24 (월)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>빅뱅</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>스타리온 45BOX 냉동냉장 / 하냉동 / 메탈 / 직냉식</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>SR-E45B2FD</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>964400</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>964400</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>1071600</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>1071600</v>
-      </c>
-      <c r="M3" s="5" t="n">
-        <v>107200</v>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>스타리온 직배송 요청</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>010-4035-1709</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>경기도 남양주시 화도읍 마석중앙로 40, 1층</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>8.24 (월)</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>빅뱅</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>스타리온 1500 냉동냉장 / 직냉식</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>SR-T15B1F</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>686700</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>686700</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>763000</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>763000</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>76300</v>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>스타리온 직배송 요청</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>010-4035-1709</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>경기도 남양주시 화도읍 마석중앙로 40, 1층</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>8.24 (월)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>빅뱅</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>스타리온 1500 올냉동 / 직냉식</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>SR-T15BAFC</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>692400</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>692400</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>769300</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>769300</v>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>76900</v>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>스타리온 직배송 요청</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>010-4035-1709</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>경기도 남양주시 화도읍 마석중앙로 40, 1층</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>8.24 (월)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>빅뱅</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>음료아날로그</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>SR-SC44RW</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>355000</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>355000</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>394500</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>394500</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>39500</v>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>스타리온 직배송 요청</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>010-4035-1709</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>경기도 남양주시 화도읍 마석중앙로 40, 1층</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
